--- a/real_data/result_table_3para.xlsx
+++ b/real_data/result_table_3para.xlsx
@@ -1,97 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BNU\BA4\毕业论文\LTRC-changepoint\real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6EA85C-06AC-42CD-B666-A531496E901F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2710" windowWidth="12190" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Estimate</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>P_value</t>
-  </si>
-  <si>
-    <t>CI_lower</t>
-  </si>
-  <si>
-    <t>CI_upper</t>
-  </si>
-  <si>
-    <t>beta1</t>
-  </si>
-  <si>
-    <t>beta2</t>
-  </si>
-  <si>
-    <t>beta3</t>
-  </si>
-  <si>
-    <t>gamma1</t>
-  </si>
-  <si>
-    <t>gamma2</t>
-  </si>
-  <si>
-    <t>gamma3</t>
-  </si>
-  <si>
-    <t>logb1</t>
-  </si>
-  <si>
-    <t>logb2</t>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI_upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logb1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logb2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -115,23 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -413,223 +381,219 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="7" width="10.90625" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.91045247230300097</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.28914200444331001</v>
-      </c>
-      <c r="D2" s="1">
-        <v>3.1488073621676298</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1.6393822360738399E-3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.34373414359411403</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47717080101189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>0.910644542428701</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.289141316524966</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.14947913142697</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00163561789761345</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.343927562039768</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.47736152281763</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>-1.3814346855690001</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.51320457158052402</v>
-      </c>
-      <c r="D3" s="1">
-        <v>-2.69178172227612</v>
-      </c>
-      <c r="E3" s="1">
-        <v>7.1071443959714502E-3</v>
-      </c>
-      <c r="F3" s="1">
-        <v>-2.3873156458668201</v>
-      </c>
-      <c r="G3" s="1">
-        <v>-0.37555372527117198</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>-1.3804342555325</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.513148686289576</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.69012528418227</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00714251987268912</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.38620568066007</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.374662830404936</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1">
-        <v>-1.65504576957592</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.17227457969482</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-1.4118243270333299</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.15800169360903399</v>
-      </c>
-      <c r="F4" s="1">
-        <v>-3.95270394577777</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.642612406625929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>-1.65792897149287</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.17337337911262</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.41295942195885</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.157667655575807</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3.9577407945536</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.641882851567865</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>1.1519735785593801</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.62521812772622398</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1.8425146800347001</v>
-      </c>
-      <c r="E5" s="1">
-        <v>6.5399901219746898E-2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-7.3453951784021601E-2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2.37740110890278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B5" t="n">
+        <v>1.15067421619138</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.625161805556611</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.84060223443574</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0656798700723791</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.0746429226995799</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.37599135508234</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1">
-        <v>1.1486126602229501</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.39239118266748</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.82492095218708095</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.40941647021827299</v>
-      </c>
-      <c r="F6" s="1">
-        <v>-1.5804740578053</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3.8776993782511999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6" t="n">
+        <v>1.15142631827065</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.39350938133358</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.826278124635757</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.408646339660064</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.57985206914318</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.88270470568447</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>-2.0855214672422302</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.77973786863656402</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-2.6746443274442102</v>
-      </c>
-      <c r="E7" s="1">
-        <v>7.4808568376757197E-3</v>
-      </c>
-      <c r="F7" s="1">
-        <v>-3.6138076897698901</v>
-      </c>
-      <c r="G7" s="1">
-        <v>-0.55723524471456298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" t="n">
+        <v>-2.08548064960889</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.779739290277212</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.67458710316811</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0074821336955212</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-3.61376965855222</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.557191640665549</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1">
-        <v>-3.16507020129279</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.520880710444655</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-6.0763820541384597</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1.2292434131985799E-9</v>
-      </c>
-      <c r="F8" s="1">
-        <v>-4.1859963937643201</v>
-      </c>
-      <c r="G8" s="1">
-        <v>-2.1441440088212702</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B8" t="n">
+        <v>-3.16506003640702</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.520891329497027</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.07623866471957</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00000000123034253289356</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-4.18600704222119</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.14411303059284</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>-4.60517018598809</v>
       </c>
-      <c r="C9" s="1">
-        <v>0.56360594293565303</v>
-      </c>
-      <c r="D9" s="1">
-        <v>-8.1709042349716103</v>
-      </c>
-      <c r="E9" s="1">
-        <v>3.0608653743397998E-16</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-5.70983783414197</v>
-      </c>
-      <c r="G9" s="1">
-        <v>-3.5005025378342101</v>
+      <c r="C9" t="n">
+        <v>0.563617523513367</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-8.17073634843944</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.000000000000000306512828065504</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-5.70986053207429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.50047983990189</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>